--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248446</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307576</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307952</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248461</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119885343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119885984</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121408352</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307572</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119885346</t>
         </is>
       </c>
     </row>
@@ -2080,6 +2145,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119885032</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2181,6 +2251,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119887119</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121408366</t>
         </is>
       </c>
     </row>
@@ -2383,6 +2463,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307609</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2482,6 +2567,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119887057</t>
         </is>
       </c>
     </row>
@@ -2629,6 +2719,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2730,6 +2825,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307555</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2829,6 +2929,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119887063</t>
         </is>
       </c>
     </row>
@@ -2932,6 +3037,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307503</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3033,6 +3143,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307600</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3134,6 +3249,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307970</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,6 +3368,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248493</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3349,6 +3474,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307522</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3450,6 +3580,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307976</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307588</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3652,6 +3792,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307943</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3766,6 +3911,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248463</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3865,6 +4015,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119885139</t>
         </is>
       </c>
     </row>
@@ -3968,6 +4123,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307534</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4085,6 +4245,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248439</t>
         </is>
       </c>
     </row>
@@ -4190,6 +4355,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307580</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119248438</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4426,6 +4601,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53735452</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4536,6 +4716,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307568</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4646,6 +4831,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307579</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4748,6 +4938,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307990</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4868,6 +5063,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405336</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4967,6 +5167,11 @@
       <c r="AY41" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121408362</t>
         </is>
       </c>
     </row>
@@ -5071,6 +5276,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112307592</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5173,6 +5383,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54468359</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5274,6 +5489,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121408368</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5375,6 +5595,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121408369</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5477,6 +5702,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54468355</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5573,8 +5803,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126537074</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>